--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{881FEF8F-8F2A-4636-8EE3-20E95F1925A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B5A463-20B4-40AB-9CE9-FC936FBA3DA6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB3082B5-1D72-4809-9BE3-C8DAD92AD81B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB3023F-4883-4CD4-8EC1-83CD67562648}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB489F17-1C37-4559-B330-2932652D3CC6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10BA4A7C-D1B8-4EB2-8795-48BBD65C26EB}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1835,22 +1835,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B5A463-20B4-40AB-9CE9-FC936FBA3DA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFBD3546-2C3E-437A-9145-A91BC5BAEF9D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB3023F-4883-4CD4-8EC1-83CD67562648}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6588F2D-43EF-4FD8-BE18-9C710D5D2551}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10BA4A7C-D1B8-4EB2-8795-48BBD65C26EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55563F7-D36E-4F77-978A-679F097C1CA7}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFBD3546-2C3E-437A-9145-A91BC5BAEF9D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49CE2575-94E7-4885-92E0-F24EF672A1D1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6588F2D-43EF-4FD8-BE18-9C710D5D2551}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A32DF84-D91E-4006-B503-3104C728AD9E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55563F7-D36E-4F77-978A-679F097C1CA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{165F954C-A871-42B5-A477-BC5A4BB44A2C}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1835,22 +1835,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B5A463-20B4-40AB-9CE9-FC936FBA3DA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D25711B4-2635-4B87-8852-6281A204E0AE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB3023F-4883-4CD4-8EC1-83CD67562648}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FB31F31-8E79-4481-A7EA-EF17B41AB5F0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10BA4A7C-D1B8-4EB2-8795-48BBD65C26EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D97E61-62AB-4118-B55C-FB7AAD3D7490}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49CE2575-94E7-4885-92E0-F24EF672A1D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{839DCE4D-C9B4-4E35-A5F1-4A08E8ADDD6F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A32DF84-D91E-4006-B503-3104C728AD9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC3B64F-24A6-48A0-80D1-D382EDCDE461}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{165F954C-A871-42B5-A477-BC5A4BB44A2C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFF1C728-0E86-41E8-B7AF-71FCFBBEB584}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{839DCE4D-C9B4-4E35-A5F1-4A08E8ADDD6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{468C904D-7FD7-409D-A676-C327E14D3E27}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC3B64F-24A6-48A0-80D1-D382EDCDE461}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{555FCC75-DCCB-49A2-987F-1A05E3E00DD8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFF1C728-0E86-41E8-B7AF-71FCFBBEB584}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68423119-C385-423D-A464-66DA14282F0F}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{468C904D-7FD7-409D-A676-C327E14D3E27}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C2DC694-F248-4A38-B5BC-4B05F6CA7370}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{555FCC75-DCCB-49A2-987F-1A05E3E00DD8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74A6F46E-D259-4E67-9991-5576CD9BAC3A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68423119-C385-423D-A464-66DA14282F0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E60692DA-4E62-452A-BAEE-A1DDB31C115E}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C2DC694-F248-4A38-B5BC-4B05F6CA7370}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A07CCE42-1D86-4E41-BEC5-FA2B0657E64F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74A6F46E-D259-4E67-9991-5576CD9BAC3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAC85BE4-5880-425F-B7F5-622C5C418424}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E60692DA-4E62-452A-BAEE-A1DDB31C115E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ADD670E-997C-4EC5-B631-FC6305140A51}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A07CCE42-1D86-4E41-BEC5-FA2B0657E64F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42ABAE35-ACEE-4445-9827-69C5A7CFC1E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAC85BE4-5880-425F-B7F5-622C5C418424}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4D6EB9E-A1E5-428F-9383-D6DB3C4D47E1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ADD670E-997C-4EC5-B631-FC6305140A51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8CD1FC4-82FE-419B-9C72-306FE8DC2C13}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42ABAE35-ACEE-4445-9827-69C5A7CFC1E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5F1D60A-416B-42E7-A895-4C34A09A25CF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4D6EB9E-A1E5-428F-9383-D6DB3C4D47E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE395EA-62F5-4D2F-9C04-107C02C65C76}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8CD1FC4-82FE-419B-9C72-306FE8DC2C13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A64EC451-54A7-485F-9DE9-DA04F859F9C3}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5F1D60A-416B-42E7-A895-4C34A09A25CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4F29EB3-61C1-4B18-84B9-3D74D668ABAF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE395EA-62F5-4D2F-9C04-107C02C65C76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F745A94-796E-472B-8AC0-6DD2A9E15C3E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A64EC451-54A7-485F-9DE9-DA04F859F9C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{307A59E0-AF43-4541-A018-8C04D6DBB67C}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4F29EB3-61C1-4B18-84B9-3D74D668ABAF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EADB7549-25A5-4CF2-B999-B5FA503F0CA6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F745A94-796E-472B-8AC0-6DD2A9E15C3E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB0C2244-9877-4D66-97E2-8FCDC2638B70}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{307A59E0-AF43-4541-A018-8C04D6DBB67C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8A4F3A1-DE6A-466E-9DAE-FC6DADAFEA00}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EADB7549-25A5-4CF2-B999-B5FA503F0CA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21E14654-A69E-4304-AE35-387A199B42E2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB0C2244-9877-4D66-97E2-8FCDC2638B70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D58D966-A005-4BDC-B25A-1A665D448215}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8A4F3A1-DE6A-466E-9DAE-FC6DADAFEA00}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{427561EB-23F6-48CD-94C7-657CADADE036}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21E14654-A69E-4304-AE35-387A199B42E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D78C252-5550-432B-941A-691C7488DEC1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D58D966-A005-4BDC-B25A-1A665D448215}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ACEAEA7-D09B-4230-A181-86FDF401CA40}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{427561EB-23F6-48CD-94C7-657CADADE036}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87B497D7-F98B-43B4-993E-1F4EF7EBDF7F}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D78C252-5550-432B-941A-691C7488DEC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5302F126-F55D-41D1-8A49-AD0058A56D84}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ACEAEA7-D09B-4230-A181-86FDF401CA40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9533AF53-ACCE-43C2-974E-8AC29AC00D1B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87B497D7-F98B-43B4-993E-1F4EF7EBDF7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E45CF5E-1485-4150-8C97-40B45D62AF8D}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5302F126-F55D-41D1-8A49-AD0058A56D84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ACD713E-C186-44E8-BDFD-A5885C45A766}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9533AF53-ACCE-43C2-974E-8AC29AC00D1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87BF6FD0-A42E-48D6-B968-0FEFD35510DF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E45CF5E-1485-4150-8C97-40B45D62AF8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F1C526A-5923-451F-A58B-6F0482DF05F6}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ACD713E-C186-44E8-BDFD-A5885C45A766}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B2599-F7F5-4C63-8C45-58934A9837C4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87BF6FD0-A42E-48D6-B968-0FEFD35510DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{630CA1E7-2AFF-48B4-BCDA-B9F52659AEE7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F1C526A-5923-451F-A58B-6F0482DF05F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14DBE8CB-4B8A-4AC7-943A-23845177AA82}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1B2599-F7F5-4C63-8C45-58934A9837C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D15E4CC-A1DB-47D4-97FF-64585C4A6B8E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{630CA1E7-2AFF-48B4-BCDA-B9F52659AEE7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12F833C-7FD6-483C-8D33-8A8090D1F15E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14DBE8CB-4B8A-4AC7-943A-23845177AA82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92DF88FE-EB55-496D-B033-DCCAAA0A50E6}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D15E4CC-A1DB-47D4-97FF-64585C4A6B8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{522C6577-657C-4D59-8C0B-5ADFBD536C4F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12F833C-7FD6-483C-8D33-8A8090D1F15E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{963728A3-6FAE-428A-89D1-7DA9B5B6620E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92DF88FE-EB55-496D-B033-DCCAAA0A50E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDF41782-A013-4001-80B4-660FDA25035E}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{522C6577-657C-4D59-8C0B-5ADFBD536C4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79DABFCE-BFE4-4E44-8337-143DE37CBC55}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{963728A3-6FAE-428A-89D1-7DA9B5B6620E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE7A0E73-24C5-4323-A640-ED282CD3992B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDF41782-A013-4001-80B4-660FDA25035E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6070A42-6197-40C9-B966-A21BC853584E}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79DABFCE-BFE4-4E44-8337-143DE37CBC55}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A67D1A43-D9CB-4E92-B06B-DDF2ABE3F620}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE7A0E73-24C5-4323-A640-ED282CD3992B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADC7B698-8F85-41F5-98FF-FE7DE7D17FFF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6070A42-6197-40C9-B966-A21BC853584E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B041BC8-244F-4E4F-B5F8-0231D376B189}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A67D1A43-D9CB-4E92-B06B-DDF2ABE3F620}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{772AF7BF-1A67-4697-9128-05302DE7C692}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADC7B698-8F85-41F5-98FF-FE7DE7D17FFF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16E9210C-941F-4F20-B6F3-FE3473F87D80}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B041BC8-244F-4E4F-B5F8-0231D376B189}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B380304B-3DE7-4C2B-96FE-E526743F1BB8}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{772AF7BF-1A67-4697-9128-05302DE7C692}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8966BC51-3CED-4F6B-A42C-EE9B93C50FA5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16E9210C-941F-4F20-B6F3-FE3473F87D80}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28DB82AD-328D-476D-9E4B-629347D8BF93}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B380304B-3DE7-4C2B-96FE-E526743F1BB8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C3BAF5B-A9F1-402F-9471-E6A0050FBB0A}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8966BC51-3CED-4F6B-A42C-EE9B93C50FA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{483FC537-A439-4BF6-8A74-B9A94C8CCFB1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28DB82AD-328D-476D-9E4B-629347D8BF93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D79CF124-EBF0-4396-9D0C-14F98B02F4EF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C3BAF5B-A9F1-402F-9471-E6A0050FBB0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8614F202-B776-49F8-9CB4-B0614D3D0EF4}"/>
 </file>